--- a/doc/presentations/2024_csqiep/aefp_visual_CS BZ v2.xlsx
+++ b/doc/presentations/2024_csqiep/aefp_visual_CS BZ v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chesun1/Library/CloudStorage/Box-Box/California Education Lab - Full Team Access/Research Projects/CSAC Survey/Gender Identities and Sexual Orientations/presentations/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christinasun/Library/CloudStorage/Dropbox/github_repos/csac/doc/presentations/2024_csqiep/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20562986-E267-6B46-8DA5-4104C95D5BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03923F0D-F258-9D4F-B553-0C200330A700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="44800" windowHeight="23000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="560" yWindow="-20620" windowWidth="34200" windowHeight="20220" firstSheet="5" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 1" sheetId="7" state="hidden" r:id="rId1"/>
@@ -28,7 +28,60 @@
     <sheet name="Worry Discrimation SO" sheetId="25" r:id="rId13"/>
     <sheet name="Worry Community" sheetId="26" r:id="rId14"/>
     <sheet name="Worry Support" sheetId="23" r:id="rId15"/>
+    <sheet name="SO queer by parent edu" sheetId="35" r:id="rId16"/>
+    <sheet name="gender queer by parent edu" sheetId="36" r:id="rId17"/>
+    <sheet name="SO x gender queer" sheetId="37" r:id="rId18"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'gender queer by parent edu'!$I$4:$I$10</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'gender queer by parent edu'!$J$3</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">'gender queer by parent edu'!$J$4:$J$10</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">'gender queer by parent edu'!$K$4:$K$10</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">'gender queer by parent edu'!$I$4:$I$10</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">'gender queer by parent edu'!$J$3</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">'gender queer by parent edu'!$J$4:$J$10</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">'gender queer by parent edu'!$K$4:$K$10</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">'gender queer by parent edu'!$I$4:$I$10</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">'gender queer by parent edu'!$J$3</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">'gender queer by parent edu'!$J$4:$J$10</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">'gender queer by parent edu'!$K$4:$K$10</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'gender queer by parent edu'!$J$4:$J$10</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'gender queer by parent edu'!$K$4:$K$10</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">'SO x gender queer'!$H$3:$H$5</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">'SO x gender queer'!$I$2</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">'SO x gender queer'!$I$3:$I$5</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">'SO x gender queer'!$J$2</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">'SO x gender queer'!$J$3:$J$5</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">'SO x gender queer'!$K$2</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'gender queer by parent edu'!$I$4:$I$10</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">'SO x gender queer'!$K$3:$K$5</definedName>
+    <definedName name="_xlchart.v1.41" hidden="1">'SO x gender queer'!$H$3:$H$5</definedName>
+    <definedName name="_xlchart.v1.42" hidden="1">'SO x gender queer'!$I$2</definedName>
+    <definedName name="_xlchart.v1.43" hidden="1">'SO x gender queer'!$I$3:$I$5</definedName>
+    <definedName name="_xlchart.v1.44" hidden="1">'SO x gender queer'!$J$2</definedName>
+    <definedName name="_xlchart.v1.45" hidden="1">'SO x gender queer'!$J$3:$J$5</definedName>
+    <definedName name="_xlchart.v1.46" hidden="1">'SO x gender queer'!$K$2</definedName>
+    <definedName name="_xlchart.v1.47" hidden="1">'SO x gender queer'!$K$3:$K$5</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'gender queer by parent edu'!$J$3</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'gender queer by parent edu'!$J$4:$J$10</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'gender queer by parent edu'!$K$4:$K$10</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">'gender queer by parent edu'!$I$4:$I$10</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">'gender queer by parent edu'!$J$3</definedName>
+    <definedName name="_xlchart.v2.20" hidden="1">'SO x gender queer'!$H$3</definedName>
+    <definedName name="_xlchart.v2.21" hidden="1">'SO x gender queer'!$H$4</definedName>
+    <definedName name="_xlchart.v2.22" hidden="1">'SO x gender queer'!$H$5</definedName>
+    <definedName name="_xlchart.v2.23" hidden="1">'SO x gender queer'!$I$2:$K$2</definedName>
+    <definedName name="_xlchart.v2.24" hidden="1">'SO x gender queer'!$I$3:$K$3</definedName>
+    <definedName name="_xlchart.v2.25" hidden="1">'SO x gender queer'!$I$4:$K$4</definedName>
+    <definedName name="_xlchart.v2.26" hidden="1">'SO x gender queer'!$I$5:$K$5</definedName>
+    <definedName name="_xlchart.v2.27" hidden="1">'SO x gender queer'!$H$3:$H$5</definedName>
+    <definedName name="_xlchart.v2.28" hidden="1">'SO x gender queer'!$I$2</definedName>
+    <definedName name="_xlchart.v2.29" hidden="1">'SO x gender queer'!$I$3:$I$5</definedName>
+    <definedName name="_xlchart.v2.30" hidden="1">'SO x gender queer'!$J$2</definedName>
+    <definedName name="_xlchart.v2.31" hidden="1">'SO x gender queer'!$J$3:$J$5</definedName>
+    <definedName name="_xlchart.v2.32" hidden="1">'SO x gender queer'!$K$2</definedName>
+    <definedName name="_xlchart.v2.33" hidden="1">'SO x gender queer'!$K$3:$K$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -46,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="110">
   <si>
     <t>Total</t>
   </si>
@@ -350,13 +403,41 @@
   <si>
     <t>Public service</t>
   </si>
+  <si>
+    <t>Sexual orientation by parent education</t>
+  </si>
+  <si>
+    <t>Some college, no degree</t>
+  </si>
+  <si>
+    <t>Graduate/Professional degree</t>
+  </si>
+  <si>
+    <t>Heterosexual</t>
+  </si>
+  <si>
+    <t>Non-heterosexual</t>
+  </si>
+  <si>
+    <t>gender by parent education</t>
+  </si>
+  <si>
+    <t>Non-cisgender`</t>
+  </si>
+  <si>
+    <t>Cisgender</t>
+  </si>
+  <si>
+    <t>Non-cisgender</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="142" x14ac:knownFonts="1">
     <font>
@@ -1195,7 +1276,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="136" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1696,6 +1777,8 @@
     <xf numFmtId="0" fontId="139" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6852,6 +6935,1895 @@
             <a:schemeClr val="tx1"/>
           </a:solidFill>
         </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Self-Reported Sexual Orientation by Parent Education</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SO queer by parent edu'!$H$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Non-heterosexual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'SO queer by parent edu'!$G$4:$G$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Did not complete high school</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>High school diploma</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Some college, no degree</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Associate degree</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Bachelor's degree</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Graduate/Professional degree</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Don't know</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SO queer by parent edu'!$H$4:$H$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.17651403249630723</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.20988446726572529</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.27650727650727652</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.24774774774774774</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24158563949139866</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.30704815073272856</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.19788918205804748</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EB4A-AE43-AE7B-D6D90EB33B39}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SO queer by parent edu'!$I$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Heterosexual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'SO queer by parent edu'!$G$4:$G$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Did not complete high school</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>High school diploma</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Some college, no degree</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Associate degree</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Bachelor's degree</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Graduate/Professional degree</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Don't know</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SO queer by parent edu'!$I$4:$I$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.75923190546528807</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.73620025673940948</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.65904365904365902</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69369369369369371</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.69035153328347043</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.6127006280530356</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.69129287598944589</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-EB4A-AE43-AE7B-D6D90EB33B39}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SO queer by parent edu'!$J$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Prefer not to say</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'SO queer by parent edu'!$G$4:$G$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Did not complete high school</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>High school diploma</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Some college, no degree</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Associate degree</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Bachelor's degree</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Graduate/Professional degree</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Don't know</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SO queer by parent edu'!$J$4:$J$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>6.4254062038404725E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.391527599486521E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.4449064449064453E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.8558558558558557E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.8062827225130892E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.0251221214235863E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.11081794195250659</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-EB4A-AE43-AE7B-D6D90EB33B39}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="849797888"/>
+        <c:axId val="849789824"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="849797888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="849789824"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="849789824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="849797888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'gender queer by parent edu'!$I$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Non-cisgender`</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'gender queer by parent edu'!$H$4:$H$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Did not complete high school</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>High school diploma</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Some college, no degree</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Associate degree</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Bachelor's degree</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Graduate/Professional degree</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Don't know</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'gender queer by parent edu'!$I$4:$I$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>3.3674963396778917E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.7375160051216392E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.3651452282157678E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.2780269058295965E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.3491827637444277E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.4947952810548224E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.6997389033942558E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5ACC-6C49-BE6E-BB4F903B983E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'gender queer by parent edu'!$J$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cisgender</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'gender queer by parent edu'!$H$4:$H$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Did not complete high school</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>High school diploma</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Some college, no degree</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Associate degree</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Bachelor's degree</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Graduate/Professional degree</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Don't know</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'gender queer by parent edu'!$J$4:$J$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.95387994143484622</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94110115236875802</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.90975103734439833</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.91928251121076232</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.9257057949479941</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.90145732130464951</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.90600522193211486</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5ACC-6C49-BE6E-BB4F903B983E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'gender queer by parent edu'!$K$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Prefer not to say</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'gender queer by parent edu'!$H$4:$H$10</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Did not complete high school</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>High school diploma</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Some college, no degree</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Associate degree</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Bachelor's degree</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Graduate/Professional degree</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Don't know</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'gender queer by parent edu'!$K$4:$K$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1.2445095168374817E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1523687580025609E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6597510373443983E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7937219730941704E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.0802377414561663E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3594725884802221E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.6997389033942558E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5ACC-6C49-BE6E-BB4F903B983E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="788357440"/>
+        <c:axId val="788354304"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="788357440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="788354304"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="788354304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="788357440"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="percentStacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SO x gender queer'!$I$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Heterosexual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'SO x gender queer'!$H$3:$H$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Cisgender</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Non-cisgender</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Prefer not to say</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SO x gender queer'!$I$3:$I$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.74562545191612439</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.6764705882352942E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.9136690647482008E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97E4-7743-8CDB-243049368E17}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SO x gender queer'!$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Non-heterosexual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'SO x gender queer'!$H$3:$H$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Cisgender</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Non-cisgender</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Prefer not to say</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SO x gender queer'!$J$3:$J$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.19190166305133768</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.90931372549019607</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.53956834532374098</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-97E4-7743-8CDB-243049368E17}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SO x gender queer'!$K$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Prefer not to say</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'SO x gender queer'!$H$3:$H$5</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Cisgender</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Non-cisgender</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Prefer not to say</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'SO x gender queer'!$K$3:$K$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>6.2472885032537964E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.3921568627450983E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.38129496402877699</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-97E4-7743-8CDB-243049368E17}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="757689728"/>
+        <c:axId val="882027456"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="757689728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="882027456"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="882027456"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="757689728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -12533,10 +14505,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent6">
-                <a:lumMod val="40000"/>
-                <a:lumOff val="60000"/>
-              </a:schemeClr>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -12545,58 +14514,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -12709,10 +14627,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
-              </a:schemeClr>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -13222,8 +15137,8 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{D29D88BA-0CF8-8A4A-8848-E63F254DD4CA}" type="CELLRANGE">
-                      <a:rPr lang="en-US" sz="2000"/>
+                    <a:fld id="{7EC42D79-8D58-FA40-9FBB-DED26B9EC257}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                           <a:solidFill>
@@ -13274,7 +15189,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{76FEE3B7-BB0F-DB47-95FB-C7D13BDCBF3C}" type="CELLRANGE">
+                    <a:fld id="{DAD00896-4BEA-CA4E-92A3-DA7CAF02A542}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13336,7 +15251,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4287F321-3B00-574D-A32B-38F57B761348}" type="CELLRANGE">
+                    <a:fld id="{754A12C3-EFCE-1D40-B958-BB75A537C342}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13370,7 +15285,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{913F563A-367E-E445-9BAD-F5044504AA01}" type="CELLRANGE">
+                    <a:fld id="{4F6F15E3-2CEF-2949-8972-03E5F3BCCF62}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13404,7 +15319,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{34A0DA11-D8F8-534C-954E-BD95EB6E350E}" type="CELLRANGE">
+                    <a:fld id="{49D603D0-3F82-944E-9569-B0220F983BDE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13438,7 +15353,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DC14715C-B6C7-AF44-9A4F-3D90725A7CA0}" type="CELLRANGE">
+                    <a:fld id="{B701580C-8493-BC44-B71F-3B04BCE4D8EC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13472,7 +15387,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{05D825BD-A17C-7149-A883-CAD53C37BBA0}" type="CELLRANGE">
+                    <a:fld id="{FB8B0C6E-CC06-B347-A6C8-8031B4F21228}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13534,7 +15449,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9D0D0C89-3F81-9C45-AAA4-9E7A84BD57F5}" type="CELLRANGE">
+                    <a:fld id="{59583C42-713F-AE44-A8BE-894CE20EAA01}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13568,7 +15483,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1310634C-A2D5-B947-9F07-BA7E2454230A}" type="CELLRANGE">
+                    <a:fld id="{4060C165-E495-D448-BFA8-B5BB564B5BFF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13602,7 +15517,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8278694A-C22A-1D40-8EBC-EFC2008AE666}" type="CELLRANGE">
+                    <a:fld id="{F1EAA122-6F7A-C241-A48B-5787ACC4097E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13636,7 +15551,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AA9BF9B7-E1AF-4741-A8A6-860CF65D7A9D}" type="CELLRANGE">
+                    <a:fld id="{171F2FA1-FE71-FF45-8F3A-911ED9E1FBB5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13670,7 +15585,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CB741903-FD68-3842-A490-1D0DA0EB154D}" type="CELLRANGE">
+                    <a:fld id="{96A69840-502E-A942-846D-FB4B66EDFE5D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13704,7 +15619,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{07D7FBA5-3043-CA44-A57A-2E56A90A4265}" type="CELLRANGE">
+                    <a:fld id="{AADA4C35-7074-3247-8E3B-494D55886EF4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14088,8 +16003,8 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{B65054F5-476E-C14F-A073-7CCF51580ED0}" type="CELLRANGE">
-                      <a:rPr lang="en-US" sz="2000"/>
+                    <a:fld id="{387BF688-2019-B74C-991D-BBB724EDD951}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                           <a:solidFill>
@@ -14140,7 +16055,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{86B6023F-B427-3540-96FE-A7823D39E08A}" type="CELLRANGE">
+                    <a:fld id="{65AB0521-9D7B-F44A-94C2-DAF8FE29CFC2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14202,7 +16117,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B336CBBB-9023-804C-A8BB-5D4A3E31E5E9}" type="CELLRANGE">
+                    <a:fld id="{2EB6C146-56CE-E74B-B365-28B2A562507A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14236,7 +16151,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FE928F9B-C075-4141-8EF4-9C0C57F82CBF}" type="CELLRANGE">
+                    <a:fld id="{3111F9DF-7A9C-A74A-A2BF-B6C96AC74E39}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14270,7 +16185,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F0368A84-EC14-DB4B-A0C2-3980E1C97D66}" type="CELLRANGE">
+                    <a:fld id="{CA5EB134-E9F5-E54C-BE45-FBCB32450054}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14304,7 +16219,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D7C6B252-EADF-8D44-B668-A5808B95120A}" type="CELLRANGE">
+                    <a:fld id="{2E97D265-F83F-8D45-893C-F12A338BF302}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14338,7 +16253,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{716B4BF5-EC3D-BA48-A638-B3BC68F1130D}" type="CELLRANGE">
+                    <a:fld id="{26A93865-8D8F-9249-A3B3-476AEB32517D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14400,7 +16315,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C93CB804-3F5D-C545-88DF-B166542F361B}" type="CELLRANGE">
+                    <a:fld id="{8AD7DFB0-1779-B744-B0F5-392D26A52FB4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14434,7 +16349,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{75B9D89E-716C-204C-BE97-F9C3F893F25F}" type="CELLRANGE">
+                    <a:fld id="{29C0D526-7667-A343-90DC-E7288EDFE423}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14468,7 +16383,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EF73025B-97A2-B049-803C-BF9CD749FEB6}" type="CELLRANGE">
+                    <a:fld id="{1B60119B-771A-0048-88CC-344532F81040}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14502,7 +16417,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5FA7951F-FAC1-104F-B0B7-335012A33C6E}" type="CELLRANGE">
+                    <a:fld id="{286EE8D2-D004-6A43-B8FA-1C6CF04D83FA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14536,7 +16451,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3E40B242-47F0-454E-948D-DEEF3CF2F54B}" type="CELLRANGE">
+                    <a:fld id="{6553EEF8-9DA2-2644-B1C3-2E625D82B733}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14570,7 +16485,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D34A83B9-413C-4C4D-BCA2-7E3B17417972}" type="CELLRANGE">
+                    <a:fld id="{5B94EAB7-F9B6-1348-8B52-C34286B49AC9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14954,8 +16869,8 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{D714BA18-B8DB-D742-8480-913CE2DD648F}" type="CELLRANGE">
-                      <a:rPr lang="en-US" sz="2000"/>
+                    <a:fld id="{27F50DB3-882D-D949-AA09-949648E9A7CE}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                           <a:solidFill>
@@ -15012,7 +16927,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5EE9C737-3468-6B47-B159-5B76CD5F6A4D}" type="CELLRANGE">
+                    <a:fld id="{09DE9878-2FF9-2D45-99FA-3FBD72A7D8A6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15074,7 +16989,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A816EA06-EC9F-CB41-8A40-6355EB725BDB}" type="CELLRANGE">
+                    <a:fld id="{7F4147A4-0041-BE41-A820-898D6044038F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15108,7 +17023,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5271DFD8-D00A-7F44-A91C-9CFAF96BC277}" type="CELLRANGE">
+                    <a:fld id="{9A3CFEE5-7470-7346-9831-4AA58EACAAFA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15142,7 +17057,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B58FA5EE-B041-FE4A-A75D-0CE993259EBC}" type="CELLRANGE">
+                    <a:fld id="{B70618EC-AE94-C34E-A8FA-BE26A60DA705}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15176,7 +17091,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{706EEA6F-B8A2-254E-AB3B-67C4EC6FC3DA}" type="CELLRANGE">
+                    <a:fld id="{95F9306C-2779-0A44-A405-A7270A7D865B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15210,7 +17125,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4F58DE34-04BC-254C-871E-3DF6A083302E}" type="CELLRANGE">
+                    <a:fld id="{B82BAA40-24BC-D64B-A279-15A38894B41B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15272,7 +17187,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B38B82F5-FB70-BC4F-8A89-C9545F3C8573}" type="CELLRANGE">
+                    <a:fld id="{3EF45C8D-FB16-8F42-AC05-A1BF840FEDEC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15306,7 +17221,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0A48E08C-4C6F-7B4F-9600-F692C4D12831}" type="CELLRANGE">
+                    <a:fld id="{3292505E-4242-6D42-85CE-56D7CF6E795C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15340,7 +17255,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9E363067-971B-FC49-BF88-16228EB1B1D9}" type="CELLRANGE">
+                    <a:fld id="{0E11EB2A-BC0A-124F-B304-C5597AD20BF3}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15374,7 +17289,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{861F36E7-8D95-B34B-BD11-8D5A5E3FDBA9}" type="CELLRANGE">
+                    <a:fld id="{E974CCCC-7FCF-A845-9DC3-58392500A9FB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15408,7 +17323,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7742D439-94CA-E649-8B65-112768AFCC5A}" type="CELLRANGE">
+                    <a:fld id="{C9DD0AE5-D92A-3645-9028-0DC97FB157D2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15442,7 +17357,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{646FDDFD-8C2B-6E4F-837A-5BD236BD3677}" type="CELLRANGE">
+                    <a:fld id="{05AE4E25-65EA-8D4B-9BD8-2919F3A6A895}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15826,7 +17741,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{87227BBB-9386-0E40-AB0F-93F78CD0BB4A}" type="CELLRANGE">
+                    <a:fld id="{F32DEA6A-F56A-F847-B0F8-D29671884905}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -15878,7 +17793,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D022337F-488B-A543-8AB0-063EDD611AF5}" type="CELLRANGE">
+                    <a:fld id="{C1B010AA-6100-F045-8E64-2860C0BAD4C2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15940,7 +17855,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B5618E92-00D7-F64E-B345-5B40F9A71E88}" type="CELLRANGE">
+                    <a:fld id="{FDEFDF52-3630-7E4C-87B9-9D592714A7EB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -15974,7 +17889,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{57769961-5818-A448-9A6C-F8AACDEBA9CB}" type="CELLRANGE">
+                    <a:fld id="{33163E59-BE8B-F04E-B540-3CD6A3CBFD73}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16008,7 +17923,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{30FB4D88-A45B-F14B-9C11-4B519BFD3CC1}" type="CELLRANGE">
+                    <a:fld id="{B66570C5-1F15-4948-9171-EBEA935896F6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16042,7 +17957,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{39C3F495-89EB-7C47-88B9-B48BFF6C4B75}" type="CELLRANGE">
+                    <a:fld id="{8A0D669B-F1B0-C046-967A-DDA38DD8B24F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16076,7 +17991,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{56B4AECA-1BBF-D14E-92B6-17A7254BDAC5}" type="CELLRANGE">
+                    <a:fld id="{5A17753E-7F45-794A-B436-C174381F6A79}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16138,7 +18053,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{09FF3788-48C0-1143-A510-EB0CFD23161C}" type="CELLRANGE">
+                    <a:fld id="{445DCF5D-CD90-6C45-8CCC-B835CB263EEE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16172,7 +18087,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{820C3CE6-F224-DC4A-9A80-6BF39F6ED420}" type="CELLRANGE">
+                    <a:fld id="{9A802526-2909-7546-8CEF-E0285C0709F8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16206,7 +18121,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FE64A61E-81BA-7A4F-A0B3-63189D33A778}" type="CELLRANGE">
+                    <a:fld id="{08024D2E-8BDE-DB49-8E8A-81AE934B624F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16240,7 +18155,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6D9A189B-2F47-5D41-A984-EBA908FBAFD9}" type="CELLRANGE">
+                    <a:fld id="{C23CDF70-D2F9-824A-809D-CFFBD5F6A4EA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16274,7 +18189,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F9E774D9-E027-5A41-B10C-269413847611}" type="CELLRANGE">
+                    <a:fld id="{EFF25793-9CA4-7E4C-90BB-1EF91C639E84}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16308,7 +18223,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6F2AD68C-5FC8-3248-8609-ADD40383208F}" type="CELLRANGE">
+                    <a:fld id="{138B03F7-E55D-8044-982A-5A0939A0D1E7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16669,7 +18584,7 @@
               <c:layout>
                 <c:manualLayout>
                   <c:x val="-9.0191196448206577E-3"/>
-                  <c:y val="-"/>
+                  <c:y val="0"/>
                 </c:manualLayout>
               </c:layout>
               <c:tx>
@@ -16692,8 +18607,8 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{8624BC94-311A-2A44-9768-2F1433D4CCC4}" type="CELLRANGE">
-                      <a:rPr lang="en-US" sz="2000"/>
+                    <a:fld id="{1EE94A3A-CBC2-1E4C-AB91-9A198355B06A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                           <a:solidFill>
@@ -16750,7 +18665,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D67F2EC9-B6B0-B746-9F3E-4296A9DCEDDD}" type="CELLRANGE">
+                    <a:fld id="{1BEC191B-F359-0F45-A264-3C0B9E54FA1D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16812,7 +18727,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B0CBC8C5-81B7-4E41-92D9-8E3F08C77329}" type="CELLRANGE">
+                    <a:fld id="{AF89CED2-F677-8240-80E0-9A065D7C388D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16846,7 +18761,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F01B914C-0CD6-3244-B8C7-92C1379C9946}" type="CELLRANGE">
+                    <a:fld id="{F03B984A-D742-E147-92F9-508D995C5FBD}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16880,7 +18795,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2257DD1B-7566-4546-B409-B4569A75FF84}" type="CELLRANGE">
+                    <a:fld id="{0933E58D-0B4A-384E-B836-45417F790D26}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16914,7 +18829,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{99687B3E-065A-9D41-8505-E18514B05E8F}" type="CELLRANGE">
+                    <a:fld id="{C930DC54-4C8F-D348-A548-3016087382B9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -16948,7 +18863,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7AB8DAEE-BF53-114B-B220-755E70313157}" type="CELLRANGE">
+                    <a:fld id="{F43FB797-7E02-8149-9EB9-9A6396D7735C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17010,7 +18925,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B6CD357A-5D9D-EC4E-8C21-313080541A7B}" type="CELLRANGE">
+                    <a:fld id="{9AA619EA-8EAB-CE49-915C-E5D81457EAED}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17044,7 +18959,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D3AAD0E4-8AFD-D244-A42B-170E58D5CBA5}" type="CELLRANGE">
+                    <a:fld id="{8B0BB74E-0DD0-6B4F-BDEC-DFFB57972F18}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17078,7 +18993,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0AC64C0D-CEA8-4247-804E-9FA1D0A123F5}" type="CELLRANGE">
+                    <a:fld id="{52E93A6C-04E6-9F48-839D-03E36EEE52AE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17112,7 +19027,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25432D37-BC8B-8742-A03F-D0713075676F}" type="CELLRANGE">
+                    <a:fld id="{F85ACC8E-293A-E646-A083-764F0DEC21E4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17146,7 +19061,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4120B4C7-3408-B74A-8147-ACE2FEC703CA}" type="CELLRANGE">
+                    <a:fld id="{CFCB9877-792D-F844-9138-1C2D8405DD57}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17180,7 +19095,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E4F0B188-CCE5-5241-8502-3CAB9B0C3C1F}" type="CELLRANGE">
+                    <a:fld id="{7EC4E420-9800-DA40-8402-D0EAB8D56F52}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17564,7 +19479,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{51C37F6B-D5D4-ED4F-85AD-C4034DB92D1C}" type="CELLRANGE">
+                    <a:fld id="{76E0FBB8-BBF1-624F-A52C-7053765165F2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -17622,7 +19537,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{46A1495B-68CD-944C-8891-C4FD91A86E14}" type="CELLRANGE">
+                    <a:fld id="{C7D03D87-8788-3F4C-BCEC-EC3B7526B7E4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17684,7 +19599,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1190EE5E-83F6-0546-AAE3-D4339F7BE295}" type="CELLRANGE">
+                    <a:fld id="{F66DE7D6-3D0D-D94B-A64E-707BDB35A677}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17718,7 +19633,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5B9B5CA2-CC65-9C40-B1CC-DD55B318227F}" type="CELLRANGE">
+                    <a:fld id="{69DD9064-EF16-AE44-BBFD-3CFB46BE8810}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17752,7 +19667,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7013C277-18B9-ED43-8E26-834B0D92DEAE}" type="CELLRANGE">
+                    <a:fld id="{72923EDC-54CD-A34F-9382-BC05245E8E2C}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17786,7 +19701,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D2638E97-7D62-2A4F-BCA0-31B063446B94}" type="CELLRANGE">
+                    <a:fld id="{138DC9CA-2DE4-2640-8585-D383D7DCF590}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17820,7 +19735,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{63CE6BD4-C179-0D4E-9B5D-84BEF70A229F}" type="CELLRANGE">
+                    <a:fld id="{EA3B8815-3F96-CE46-8AC9-88EFA38DEABC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17882,7 +19797,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{33DC2387-7EC9-0A4D-BA7F-8364DAD27720}" type="CELLRANGE">
+                    <a:fld id="{EF03FCB4-9B98-814E-8C92-8518E1C7C936}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17916,7 +19831,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{19CC7DC6-00A3-8943-83F9-7EC6CA72B339}" type="CELLRANGE">
+                    <a:fld id="{CC9878F1-8CA5-9A4F-AF03-F71F2737D828}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17950,7 +19865,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E32F078F-8B72-EA47-A3CB-A34C5C39F3B6}" type="CELLRANGE">
+                    <a:fld id="{642B8FF8-4824-9445-BD64-C20C8E512958}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -17984,7 +19899,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5807110C-491A-2042-855F-F08E68FCA607}" type="CELLRANGE">
+                    <a:fld id="{2A27D129-B5B6-8247-AFEC-098462BF8207}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18018,7 +19933,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{299EB4C2-E0DD-D04B-AE09-17A69DA3E444}" type="CELLRANGE">
+                    <a:fld id="{C2D924A5-F206-EB40-B866-D9EFDA17019D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18052,7 +19967,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3535CE9F-3E4D-6048-8260-53CAAF3DAF98}" type="CELLRANGE">
+                    <a:fld id="{FCAF43F2-A7C1-534F-B7EF-7435C1832373}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18418,7 +20333,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C56E878D-ADF8-204B-A1F7-026B05553E06}" type="CELLRANGE">
+                    <a:fld id="{D7F13A5A-3D42-8148-A85E-D03EAA6009AB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18451,7 +20366,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{13176369-9EB0-EC45-B466-ECB99B313B2D}" type="CELLRANGE">
+                    <a:fld id="{EB0CF89A-945F-CB45-B16C-B7570B21E012}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18513,7 +20428,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{45CE7DA3-795B-6E45-AC5C-F58C0E11A55A}" type="CELLRANGE">
+                    <a:fld id="{5062164F-F869-4147-9710-71D111B721B2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18547,7 +20462,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{27D2CBFB-3DA7-CE40-A629-4B7E9B375F12}" type="CELLRANGE">
+                    <a:fld id="{596F7F24-CDDD-E04F-A4B1-E62BB8F2C62F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18581,7 +20496,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4E70A597-15F5-3840-8EC5-64BC01D15A05}" type="CELLRANGE">
+                    <a:fld id="{7EEAFC69-A71A-5048-BA39-949A4713709A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18615,7 +20530,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DE46B94C-EC78-3841-9E50-64BD84997E1C}" type="CELLRANGE">
+                    <a:fld id="{317C6EFA-792E-204C-8BDA-007E63EE2DD8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18649,7 +20564,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EB8899C3-5A60-4A43-943D-55000369318F}" type="CELLRANGE">
+                    <a:fld id="{0DC97E51-5432-3B44-A0FA-8AAD39E961FA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18711,7 +20626,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EB34CF66-BFD8-6B43-8740-6F546D621DA5}" type="CELLRANGE">
+                    <a:fld id="{C316967D-13A6-9140-B0E0-1DFA1CD86275}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18745,7 +20660,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{532E6594-6CB9-8341-9DC1-5359F3D7EA52}" type="CELLRANGE">
+                    <a:fld id="{816EFCC1-C762-8041-A1D1-304DD6C3572A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18779,7 +20694,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C78E2B46-63BC-044C-A374-9A7C47931FBF}" type="CELLRANGE">
+                    <a:fld id="{0D9BC431-F451-AA47-983A-C147E397F3D1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18813,7 +20728,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{38C376F5-9C8B-044B-8AD3-DCD7E9DF482B}" type="CELLRANGE">
+                    <a:fld id="{CEE3A146-7D2B-394C-B1BA-D250D14B3F56}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18847,7 +20762,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{707C91CC-CAF1-B24D-A23B-DC800642F4E3}" type="CELLRANGE">
+                    <a:fld id="{C6CBEB6E-3F2F-D64E-B126-E8908AD43497}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -18881,7 +20796,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0DC2B8DC-9CB0-C44C-96ED-520D7FC2F710}" type="CELLRANGE">
+                    <a:fld id="{E66A590A-2160-B44B-A874-0B47EBFC2F7D}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19265,7 +21180,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{63FA5F80-835B-964D-A4DA-A53CAC1F86E9}" type="CELLRANGE">
+                    <a:fld id="{6E6507B8-FDC2-404E-AE4D-3DCEA2BCAEEC}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -19323,7 +21238,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{671D92DD-CDF5-B748-BB18-1EA069CC6F84}" type="CELLRANGE">
+                    <a:fld id="{0CF7F3EE-F77F-7242-A10F-376AF27A450A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19385,7 +21300,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F32613FD-6252-6B4B-A445-A7FC43B28D12}" type="CELLRANGE">
+                    <a:fld id="{E5B9F0E0-C4A6-AD4C-A77F-6015A02F7599}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19419,7 +21334,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8F1A73AD-0E8E-BF49-8F39-DDDBAEE67423}" type="CELLRANGE">
+                    <a:fld id="{5C588AA4-35F7-0D45-93AB-74075CF4DC06}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19453,7 +21368,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4B94286A-8B47-2C43-9D2E-1E092EBACA17}" type="CELLRANGE">
+                    <a:fld id="{3A3A927A-E504-DE4D-B792-1BD21C359641}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19487,7 +21402,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{96C5E7EB-B9F8-BE4E-B79E-6F0684703E56}" type="CELLRANGE">
+                    <a:fld id="{8DCB836F-F055-4E41-9868-7F4DEDDBA092}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19521,7 +21436,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4B06A49A-6C81-594C-A5BB-D1ADD00060B1}" type="CELLRANGE">
+                    <a:fld id="{3FCB0F4B-1F9B-074C-BD08-CC4F7369D46B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19583,7 +21498,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8BB4C42E-8E50-434B-97F6-F8ACB6349D67}" type="CELLRANGE">
+                    <a:fld id="{393E2D8C-316B-5D46-92CE-43E178B6FC58}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19617,7 +21532,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B4E25DF2-A5F2-AE4D-B61E-C450A09A666F}" type="CELLRANGE">
+                    <a:fld id="{96F7EB78-31B5-D04B-910F-CA56426777A9}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19651,7 +21566,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4AA923E9-2C3E-F246-B413-FE8F640E3419}" type="CELLRANGE">
+                    <a:fld id="{43AF798F-14EA-1E44-9EF6-939EE1DEE9D0}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19685,7 +21600,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B7499F2F-3077-BF4A-9A09-E2A178FADCBA}" type="CELLRANGE">
+                    <a:fld id="{B612081D-94A9-E341-8CBC-2720AF4CC9D2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19719,7 +21634,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C9C4A828-97F8-9C44-AA1A-50E7CD43CDF9}" type="CELLRANGE">
+                    <a:fld id="{F6E02F68-A1D3-224D-9D5F-861FFD79A37B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -19753,7 +21668,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B33BEDF0-B378-1D43-93CE-A1BD66CA3585}" type="CELLRANGE">
+                    <a:fld id="{50583167-4FB3-0F43-987C-7913DBF260CA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20137,7 +22052,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{DB1A21F2-3503-8542-B157-5FB98A8624C9}" type="CELLRANGE">
+                    <a:fld id="{A09AF5B5-FE6C-AD48-BF69-CB1DD7721194}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -20195,7 +22110,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{13DAB75E-B196-934F-83AA-99F078EDB67D}" type="CELLRANGE">
+                    <a:fld id="{436B4085-3942-224E-84D2-3485A1C5DE62}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20257,7 +22172,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A2279A34-C38B-1145-B335-B1789DBA905A}" type="CELLRANGE">
+                    <a:fld id="{DD9F89D5-FE00-644D-BBBE-EA3C2A04BC19}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20291,7 +22206,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D7209864-1DCD-3E46-9083-FE211F629959}" type="CELLRANGE">
+                    <a:fld id="{072B13A7-52C3-BD44-B9B8-966DF41E24CF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20325,7 +22240,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6239D74A-8A55-CA4D-91D4-A924878DA336}" type="CELLRANGE">
+                    <a:fld id="{598475D5-7532-F145-9C58-B6FA13C0CC4A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20359,7 +22274,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5017CCC5-1A66-864F-954A-1C5E3BC10044}" type="CELLRANGE">
+                    <a:fld id="{C4F2ABEE-22B2-B14B-9075-732523ACDC56}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20393,7 +22308,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BEC59BED-B3F0-5C44-B027-FBF52E6F4D8D}" type="CELLRANGE">
+                    <a:fld id="{4EF99673-6882-4A40-90DE-4B6E0C875542}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20455,7 +22370,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BC3DBECA-A138-D949-9F9D-8737E84ED9C0}" type="CELLRANGE">
+                    <a:fld id="{C1857B3C-D0A5-1F4D-912C-19E36AF1D0B6}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20489,7 +22404,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7340F32F-9547-A04F-AB72-5376CFDFE07A}" type="CELLRANGE">
+                    <a:fld id="{F27B9A7D-EBBE-B24F-A54B-CD5B678B7779}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20523,7 +22438,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8DED7FF0-DD35-A240-BE58-4EAF4F77E200}" type="CELLRANGE">
+                    <a:fld id="{8814AC38-FD93-7D43-ABAC-7391C09C5C7E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20557,7 +22472,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{741718AF-A70C-AB49-9C39-6212FD98FE98}" type="CELLRANGE">
+                    <a:fld id="{8A5982F1-9098-EB4F-9A0E-D30C756EC99A}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20591,7 +22506,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D3BED254-0086-8141-ACCE-AFA2AE1E1442}" type="CELLRANGE">
+                    <a:fld id="{87147BDC-1E43-F54C-B9AC-D524D2B4D960}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -20625,7 +22540,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{65BD64D8-7AB1-E44E-8AF2-EA2146DBB16F}" type="CELLRANGE">
+                    <a:fld id="{9D3A5C55-3AF0-8F43-95BF-E77D03681152}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21008,8 +22923,8 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{E09CE67D-F1C3-6946-AD2D-726EE0968D76}" type="CELLRANGE">
-                      <a:rPr lang="en-US" sz="2000"/>
+                    <a:fld id="{106A3B3E-782B-CB42-9392-A44B010186D9}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
                       <a:pPr>
                         <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                           <a:solidFill>
@@ -21060,7 +22975,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D0A9C8CC-06E6-2B49-A732-C6F5B97FD543}" type="CELLRANGE">
+                    <a:fld id="{1BBA0C34-F687-9C4C-A65C-AE13E63FEC40}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21122,7 +23037,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C8892675-BCEB-8F48-B9B2-98566A73EB8E}" type="CELLRANGE">
+                    <a:fld id="{A26C89D6-5FEF-4249-B2C3-E44FA1118B28}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21156,7 +23071,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AA7D4C71-D638-A44C-82EE-056EE7E43A2E}" type="CELLRANGE">
+                    <a:fld id="{94B2DC1B-4464-AB48-B7A3-BBE47498758B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21190,7 +23105,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B1129846-D7FA-404B-B285-BD4B43EE17B5}" type="CELLRANGE">
+                    <a:fld id="{6FC59789-B01E-C24C-AEA7-691C304AA9C1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21224,7 +23139,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ECF664DA-D537-AA46-9398-DC7DDE824343}" type="CELLRANGE">
+                    <a:fld id="{E58572CB-A9CA-3B4B-A5A2-2B698A134ECE}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21258,7 +23173,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2B2F5C59-7D2E-C448-B82B-64D48834304F}" type="CELLRANGE">
+                    <a:fld id="{F9C473C3-501D-2C45-9647-C232C08616DA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21320,7 +23235,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{052F0F1F-C56B-CC4C-B997-FCEBC4E39780}" type="CELLRANGE">
+                    <a:fld id="{E82695BA-6DCF-EC4E-A27D-3996A549F7B4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21354,7 +23269,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{500F5611-6E73-244B-94BD-06751EF0A7A8}" type="CELLRANGE">
+                    <a:fld id="{8F8F6A4B-3192-C140-93E1-E3D9A75B3DF5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21388,7 +23303,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4D6A1B00-F3CD-E64B-85B2-74BEE4B67A5F}" type="CELLRANGE">
+                    <a:fld id="{A037AD63-6ACE-CD47-9337-20F7934291D1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21422,7 +23337,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7D67BD26-E1CF-9B4D-A587-3D9476AEC2EA}" type="CELLRANGE">
+                    <a:fld id="{5E7B7101-E987-EF43-A2D0-DF8B274A49F1}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21456,7 +23371,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C6BD9A51-E315-D14A-B621-263DC498BC05}" type="CELLRANGE">
+                    <a:fld id="{4FBBE869-CBA0-DC44-A2BD-0A7CFD90CC33}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21490,7 +23405,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8304EEAE-1032-4E41-AEBB-FDF98AF7B91D}" type="CELLRANGE">
+                    <a:fld id="{4A39676C-7667-8A4A-A5ED-EC147C9C083F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -21871,6 +23786,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -22962,6 +24997,1521 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -27116,6 +30666,129 @@
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>796191</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>185615</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19539</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>87924</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55B43CA6-5C3C-D76B-E66F-F635D8B5879A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3C6E9B6-046C-7C08-C35B-5C2790D1F150}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>736600</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68E2B1A6-312E-A302-7A25-F1D69BC83DEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -27473,47 +31146,47 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Custom 1">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="4F271C"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E7DEC9"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="004C84"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="FFBF00"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="C32D2E"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="446E27"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="964305"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="3891A7"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="8DC765"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="AA8A14"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -27619,7 +31292,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -27761,7 +31434,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -31202,6 +34875,698 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{335DB8E9-4C65-274C-83C1-E569222AA84B}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B3" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>239</v>
+      </c>
+      <c r="C4">
+        <v>1028</v>
+      </c>
+      <c r="D4">
+        <v>87</v>
+      </c>
+      <c r="E4">
+        <v>1354</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="192">
+        <f>B4/$E4</f>
+        <v>0.17651403249630723</v>
+      </c>
+      <c r="I4" s="192">
+        <f>C4/$E4</f>
+        <v>0.75923190546528807</v>
+      </c>
+      <c r="J4" s="192">
+        <f>D4/$E4</f>
+        <v>6.4254062038404725E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>327</v>
+      </c>
+      <c r="C5">
+        <v>1147</v>
+      </c>
+      <c r="D5">
+        <v>84</v>
+      </c>
+      <c r="E5">
+        <v>1558</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="192">
+        <f>B5/$E5</f>
+        <v>0.20988446726572529</v>
+      </c>
+      <c r="I5" s="192">
+        <f>C5/$E5</f>
+        <v>0.73620025673940948</v>
+      </c>
+      <c r="J5" s="192">
+        <f>D5/$E5</f>
+        <v>5.391527599486521E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6">
+        <v>266</v>
+      </c>
+      <c r="C6">
+        <v>634</v>
+      </c>
+      <c r="D6">
+        <v>62</v>
+      </c>
+      <c r="E6">
+        <v>962</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="192">
+        <f>B6/$E6</f>
+        <v>0.27650727650727652</v>
+      </c>
+      <c r="I6" s="192">
+        <f>C6/$E6</f>
+        <v>0.65904365904365902</v>
+      </c>
+      <c r="J6" s="192">
+        <f>D6/$E6</f>
+        <v>6.4449064449064453E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>110</v>
+      </c>
+      <c r="C7">
+        <v>308</v>
+      </c>
+      <c r="D7">
+        <v>26</v>
+      </c>
+      <c r="E7">
+        <v>444</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="192">
+        <f>B7/$E7</f>
+        <v>0.24774774774774774</v>
+      </c>
+      <c r="I7" s="192">
+        <f>C7/$E7</f>
+        <v>0.69369369369369371</v>
+      </c>
+      <c r="J7" s="192">
+        <f>D7/$E7</f>
+        <v>5.8558558558558557E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>323</v>
+      </c>
+      <c r="C8">
+        <v>923</v>
+      </c>
+      <c r="D8">
+        <v>91</v>
+      </c>
+      <c r="E8">
+        <v>1337</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="192">
+        <f>B8/$E8</f>
+        <v>0.24158563949139866</v>
+      </c>
+      <c r="I8" s="192">
+        <f>C8/$E8</f>
+        <v>0.69035153328347043</v>
+      </c>
+      <c r="J8" s="192">
+        <f>D8/$E8</f>
+        <v>6.8062827225130892E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9">
+        <v>440</v>
+      </c>
+      <c r="C9">
+        <v>878</v>
+      </c>
+      <c r="D9">
+        <v>115</v>
+      </c>
+      <c r="E9">
+        <v>1433</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="192">
+        <f>B9/$E9</f>
+        <v>0.30704815073272856</v>
+      </c>
+      <c r="I9" s="192">
+        <f>C9/$E9</f>
+        <v>0.6127006280530356</v>
+      </c>
+      <c r="J9" s="192">
+        <f>D9/$E9</f>
+        <v>8.0251221214235863E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>75</v>
+      </c>
+      <c r="C10">
+        <v>262</v>
+      </c>
+      <c r="D10">
+        <v>42</v>
+      </c>
+      <c r="E10">
+        <v>379</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="192">
+        <f>B10/$E10</f>
+        <v>0.19788918205804748</v>
+      </c>
+      <c r="I10" s="192">
+        <f>C10/$E10</f>
+        <v>0.69129287598944589</v>
+      </c>
+      <c r="J10" s="192">
+        <f>D10/$E10</f>
+        <v>0.11081794195250659</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <f>SUM(E4:E10)</f>
+        <v>7467</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BEE8EC-3DEE-C04E-B2A1-133022BD61A8}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B3" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>46</v>
+      </c>
+      <c r="C4">
+        <v>1303</v>
+      </c>
+      <c r="D4">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <f>SUM(B4:D4)</f>
+        <v>1366</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="193">
+        <f>B4/$E4</f>
+        <v>3.3674963396778917E-2</v>
+      </c>
+      <c r="J4" s="193">
+        <f t="shared" ref="J4:K10" si="0">C4/$E4</f>
+        <v>0.95387994143484622</v>
+      </c>
+      <c r="K4" s="193">
+        <f t="shared" si="0"/>
+        <v>1.2445095168374817E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>74</v>
+      </c>
+      <c r="C5">
+        <v>1470</v>
+      </c>
+      <c r="D5">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <f t="shared" ref="E5:E10" si="1">SUM(B5:D5)</f>
+        <v>1562</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="193">
+        <f t="shared" ref="I5:I10" si="2">B5/$E5</f>
+        <v>4.7375160051216392E-2</v>
+      </c>
+      <c r="J5" s="193">
+        <f t="shared" si="0"/>
+        <v>0.94110115236875802</v>
+      </c>
+      <c r="K5" s="193">
+        <f t="shared" si="0"/>
+        <v>1.1523687580025609E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6">
+        <v>71</v>
+      </c>
+      <c r="C6">
+        <v>877</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>964</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="193">
+        <f t="shared" si="2"/>
+        <v>7.3651452282157678E-2</v>
+      </c>
+      <c r="J6" s="193">
+        <f t="shared" si="0"/>
+        <v>0.90975103734439833</v>
+      </c>
+      <c r="K6" s="193">
+        <f t="shared" si="0"/>
+        <v>1.6597510373443983E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7">
+        <v>410</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>446</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="193">
+        <f t="shared" si="2"/>
+        <v>6.2780269058295965E-2</v>
+      </c>
+      <c r="J7" s="193">
+        <f t="shared" si="0"/>
+        <v>0.91928251121076232</v>
+      </c>
+      <c r="K7" s="193">
+        <f t="shared" si="0"/>
+        <v>1.7937219730941704E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>72</v>
+      </c>
+      <c r="C8">
+        <v>1246</v>
+      </c>
+      <c r="D8">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>1346</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="193">
+        <f t="shared" si="2"/>
+        <v>5.3491827637444277E-2</v>
+      </c>
+      <c r="J8" s="193">
+        <f t="shared" si="0"/>
+        <v>0.9257057949479941</v>
+      </c>
+      <c r="K8" s="193">
+        <f t="shared" si="0"/>
+        <v>2.0802377414561663E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9">
+        <v>108</v>
+      </c>
+      <c r="C9">
+        <v>1299</v>
+      </c>
+      <c r="D9">
+        <v>34</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>1441</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="193">
+        <f t="shared" si="2"/>
+        <v>7.4947952810548224E-2</v>
+      </c>
+      <c r="J9" s="193">
+        <f t="shared" si="0"/>
+        <v>0.90145732130464951</v>
+      </c>
+      <c r="K9" s="193">
+        <f t="shared" si="0"/>
+        <v>2.3594725884802221E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>18</v>
+      </c>
+      <c r="C10">
+        <v>347</v>
+      </c>
+      <c r="D10">
+        <v>18</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>383</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="193">
+        <f t="shared" si="2"/>
+        <v>4.6997389033942558E-2</v>
+      </c>
+      <c r="J10" s="193">
+        <f t="shared" si="0"/>
+        <v>0.90600522193211486</v>
+      </c>
+      <c r="K10" s="193">
+        <f t="shared" si="0"/>
+        <v>4.6997389033942558E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <f>SUM(E4:E10)</f>
+        <v>7508</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFB82DE-AD93-6645-94AB-AF1A045BFCBE}">
+  <dimension ref="A2:K5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3">
+        <v>5156</v>
+      </c>
+      <c r="C3">
+        <v>1327</v>
+      </c>
+      <c r="D3">
+        <v>432</v>
+      </c>
+      <c r="E3">
+        <f>SUM(B3:D3)</f>
+        <v>6915</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="192">
+        <f>B3/$E3</f>
+        <v>0.74562545191612439</v>
+      </c>
+      <c r="J3" s="192">
+        <f t="shared" ref="J3:K5" si="0">C3/$E3</f>
+        <v>0.19190166305133768</v>
+      </c>
+      <c r="K3" s="192">
+        <f t="shared" si="0"/>
+        <v>6.2472885032537964E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>371</v>
+      </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E5" si="1">SUM(B4:D4)</f>
+        <v>408</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="192">
+        <f t="shared" ref="I4:I5" si="2">B4/$E4</f>
+        <v>3.6764705882352942E-2</v>
+      </c>
+      <c r="J4" s="192">
+        <f t="shared" si="0"/>
+        <v>0.90931372549019607</v>
+      </c>
+      <c r="K4" s="192">
+        <f t="shared" si="0"/>
+        <v>5.3921568627450983E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>75</v>
+      </c>
+      <c r="D5">
+        <v>53</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="192">
+        <f t="shared" si="2"/>
+        <v>7.9136690647482008E-2</v>
+      </c>
+      <c r="J5" s="192">
+        <f t="shared" si="0"/>
+        <v>0.53956834532374098</v>
+      </c>
+      <c r="K5" s="192">
+        <f t="shared" si="0"/>
+        <v>0.38129496402877699</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1D0EE1-D47C-8E46-A82E-56FC256A6245}">
   <dimension ref="A1:G25"/>
